--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
   <si>
     <t>49018</t>
   </si>
@@ -130,15 +130,6 @@
     <t>AE5E440103256CB9AA342C48907BFF85</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
     <t>Cuadro general de clasificación archivística</t>
   </si>
   <si>
@@ -172,27 +163,6 @@
     <t>885140</t>
   </si>
   <si>
-    <t>1626790</t>
-  </si>
-  <si>
-    <t>1848767</t>
-  </si>
-  <si>
-    <t>2079885</t>
-  </si>
-  <si>
-    <t>1353810</t>
-  </si>
-  <si>
-    <t>3012233</t>
-  </si>
-  <si>
-    <t>3012234</t>
-  </si>
-  <si>
-    <t>3012235</t>
-  </si>
-  <si>
     <t>Dictamen y acta de baja documental y transferencia secundaria</t>
   </si>
   <si>
@@ -244,7 +214,7 @@
     <t>Segundo apellido</t>
   </si>
   <si>
-    <t>Puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Cargo</t>
@@ -317,42 +287,6 @@
   </si>
   <si>
     <t>Capturista</t>
-  </si>
-  <si>
-    <t>785013A4D09C419F11771D1EBA4BB3AB</t>
-  </si>
-  <si>
-    <t>3EA40E1D964DE660086694F473156C90</t>
-  </si>
-  <si>
-    <t>56A4AF979F0554F2FD5E20C2E9EA6365</t>
-  </si>
-  <si>
-    <t>Surisadai</t>
-  </si>
-  <si>
-    <t>35CA7E5D86D05B6CDD40C89B14123758</t>
-  </si>
-  <si>
-    <t>ED39F626C58EF0044627FEA2A4BDE1C8</t>
-  </si>
-  <si>
-    <t>Nestor</t>
-  </si>
-  <si>
-    <t>Ahuatzi</t>
-  </si>
-  <si>
-    <t>Flores</t>
-  </si>
-  <si>
-    <t>Jefe de Oficina</t>
-  </si>
-  <si>
-    <t>515868DA600EBA8387204785EBC6155A</t>
-  </si>
-  <si>
-    <t>BBEE0012F9AB75BDDDA074AD2E5125AA</t>
   </si>
 </sst>
 </file>
@@ -429,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -446,6 +380,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -916,35 +853,35 @@
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45017</v>
+      </c>
+      <c r="D8" s="7">
+        <v>45291</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -958,7 +895,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E178">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E197">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -973,52 +910,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1028,15 +965,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1059,316 +996,155 @@
     </row>
     <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
